--- a/app/database/MSI_database_V1.0.xlsx
+++ b/app/database/MSI_database_V1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/u0065634/Documents/Software_projects/msi-quant/app/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340053CE-CC56-634C-B7E5-13D393D9C8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BDB51B1-0DAA-AC4B-8E89-824CE81C326F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34180" yWindow="1440" windowWidth="31520" windowHeight="19080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10107" uniqueCount="3747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10107" uniqueCount="3749">
   <si>
     <t>ID</t>
   </si>
@@ -11274,6 +11274,12 @@
   </si>
   <si>
     <t>SHex2Cer 44:4;O2</t>
+  </si>
+  <si>
+    <t>PC-O/PC-P</t>
+  </si>
+  <si>
+    <t>PE-O/PE-P</t>
   </si>
 </sst>
 </file>
@@ -11651,7 +11657,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="42.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.5" bestFit="1" customWidth="1"/>
@@ -13807,7 +13813,7 @@
         <v>935</v>
       </c>
       <c r="C91" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>873</v>
@@ -13825,7 +13831,7 @@
         <v>855</v>
       </c>
       <c r="C92" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>866</v>
@@ -13846,7 +13852,7 @@
         <v>856</v>
       </c>
       <c r="C93" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>867</v>
@@ -13866,7 +13872,7 @@
         <v>857</v>
       </c>
       <c r="C94" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>868</v>
@@ -13886,7 +13892,7 @@
         <v>858</v>
       </c>
       <c r="C95" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>869</v>
@@ -13906,7 +13912,7 @@
         <v>859</v>
       </c>
       <c r="C96" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>870</v>
@@ -13926,7 +13932,7 @@
         <v>860</v>
       </c>
       <c r="C97" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D97" s="6" t="s">
         <v>871</v>
@@ -13946,7 +13952,7 @@
         <v>861</v>
       </c>
       <c r="C98" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>872</v>
@@ -13966,7 +13972,7 @@
         <v>862</v>
       </c>
       <c r="C99" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>873</v>
@@ -13986,7 +13992,7 @@
         <v>956</v>
       </c>
       <c r="C100" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>874</v>
@@ -14008,7 +14014,7 @@
         <v>957</v>
       </c>
       <c r="C101" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>875</v>
@@ -14030,7 +14036,7 @@
         <v>958</v>
       </c>
       <c r="C102" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>876</v>
@@ -14052,7 +14058,7 @@
         <v>959</v>
       </c>
       <c r="C103" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D103" s="6" t="s">
         <v>877</v>
@@ -14074,7 +14080,7 @@
         <v>960</v>
       </c>
       <c r="C104" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>878</v>
@@ -14096,7 +14102,7 @@
         <v>961</v>
       </c>
       <c r="C105" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>879</v>
@@ -14118,7 +14124,7 @@
         <v>863</v>
       </c>
       <c r="C106" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>880</v>
@@ -14138,8 +14144,8 @@
       <c r="B107" s="6" t="s">
         <v>936</v>
       </c>
-      <c r="C107" s="6" t="s">
-        <v>2</v>
+      <c r="C107" t="s">
+        <v>3747</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>946</v>
@@ -14157,7 +14163,7 @@
         <v>962</v>
       </c>
       <c r="C108" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>881</v>
@@ -14174,8 +14180,8 @@
       <c r="B109" s="6" t="s">
         <v>937</v>
       </c>
-      <c r="C109" s="6" t="s">
-        <v>2</v>
+      <c r="C109" t="s">
+        <v>3747</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>947</v>
@@ -14193,7 +14199,7 @@
         <v>963</v>
       </c>
       <c r="C110" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>882</v>
@@ -14211,7 +14217,7 @@
         <v>964</v>
       </c>
       <c r="C111" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>883</v>
@@ -14232,7 +14238,7 @@
         <v>965</v>
       </c>
       <c r="C112" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>884</v>
@@ -14253,7 +14259,7 @@
         <v>966</v>
       </c>
       <c r="C113" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>885</v>
@@ -14274,7 +14280,7 @@
         <v>967</v>
       </c>
       <c r="C114" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>886</v>
@@ -14295,7 +14301,7 @@
         <v>968</v>
       </c>
       <c r="C115" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>887</v>
@@ -14316,7 +14322,7 @@
         <v>969</v>
       </c>
       <c r="C116" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>888</v>
@@ -14337,7 +14343,7 @@
         <v>864</v>
       </c>
       <c r="C117" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>889</v>
@@ -14354,8 +14360,8 @@
       <c r="B118" s="6" t="s">
         <v>938</v>
       </c>
-      <c r="C118" s="6" t="s">
-        <v>2</v>
+      <c r="C118" t="s">
+        <v>3747</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>948</v>
@@ -14373,7 +14379,7 @@
         <v>970</v>
       </c>
       <c r="C119" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D119" s="6" t="s">
         <v>890</v>
@@ -14397,7 +14403,7 @@
         <v>971</v>
       </c>
       <c r="C120" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>891</v>
@@ -14421,7 +14427,7 @@
         <v>972</v>
       </c>
       <c r="C121" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>892</v>
@@ -14445,7 +14451,7 @@
         <v>973</v>
       </c>
       <c r="C122" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D122" s="6" t="s">
         <v>893</v>
@@ -14469,7 +14475,7 @@
         <v>974</v>
       </c>
       <c r="C123" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D123" s="6" t="s">
         <v>894</v>
@@ -14493,7 +14499,7 @@
         <v>975</v>
       </c>
       <c r="C124" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>895</v>
@@ -14517,7 +14523,7 @@
         <v>976</v>
       </c>
       <c r="C125" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D125" s="6" t="s">
         <v>896</v>
@@ -14541,7 +14547,7 @@
         <v>977</v>
       </c>
       <c r="C126" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>897</v>
@@ -14565,7 +14571,7 @@
         <v>978</v>
       </c>
       <c r="C127" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>898</v>
@@ -14589,7 +14595,7 @@
         <v>979</v>
       </c>
       <c r="C128" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>899</v>
@@ -14613,7 +14619,7 @@
         <v>980</v>
       </c>
       <c r="C129" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>900</v>
@@ -14637,7 +14643,7 @@
         <v>981</v>
       </c>
       <c r="C130" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>901</v>
@@ -14661,7 +14667,7 @@
         <v>982</v>
       </c>
       <c r="C131" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>902</v>
@@ -14680,8 +14686,8 @@
       <c r="B132" s="6" t="s">
         <v>939</v>
       </c>
-      <c r="C132" s="6" t="s">
-        <v>2</v>
+      <c r="C132" t="s">
+        <v>3747</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>949</v>
@@ -14703,7 +14709,7 @@
         <v>983</v>
       </c>
       <c r="C133" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>903</v>
@@ -14724,7 +14730,7 @@
         <v>984</v>
       </c>
       <c r="C134" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>904</v>
@@ -14748,7 +14754,7 @@
         <v>985</v>
       </c>
       <c r="C135" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>905</v>
@@ -14772,7 +14778,7 @@
         <v>986</v>
       </c>
       <c r="C136" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>906</v>
@@ -14796,7 +14802,7 @@
         <v>987</v>
       </c>
       <c r="C137" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>907</v>
@@ -14820,7 +14826,7 @@
         <v>865</v>
       </c>
       <c r="C138" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>908</v>
@@ -14844,7 +14850,7 @@
         <v>988</v>
       </c>
       <c r="C139" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>909</v>
@@ -14865,8 +14871,8 @@
       <c r="B140" s="6" t="s">
         <v>940</v>
       </c>
-      <c r="C140" s="6" t="s">
-        <v>2</v>
+      <c r="C140" t="s">
+        <v>3747</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>950</v>
@@ -14888,7 +14894,7 @@
         <v>989</v>
       </c>
       <c r="C141" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>910</v>
@@ -14912,7 +14918,7 @@
         <v>990</v>
       </c>
       <c r="C142" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>911</v>
@@ -14936,7 +14942,7 @@
         <v>991</v>
       </c>
       <c r="C143" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D143" s="6" t="s">
         <v>912</v>
@@ -14960,7 +14966,7 @@
         <v>992</v>
       </c>
       <c r="C144" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>913</v>
@@ -14984,7 +14990,7 @@
         <v>993</v>
       </c>
       <c r="C145" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D145" s="6" t="s">
         <v>914</v>
@@ -15008,7 +15014,7 @@
         <v>994</v>
       </c>
       <c r="C146" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D146" s="6" t="s">
         <v>915</v>
@@ -15030,7 +15036,7 @@
         <v>995</v>
       </c>
       <c r="C147" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D147" s="6" t="s">
         <v>916</v>
@@ -15054,7 +15060,7 @@
         <v>996</v>
       </c>
       <c r="C148" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>917</v>
@@ -15078,7 +15084,7 @@
         <v>997</v>
       </c>
       <c r="C149" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D149" s="6" t="s">
         <v>918</v>
@@ -15102,7 +15108,7 @@
         <v>998</v>
       </c>
       <c r="C150" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D150" s="6" t="s">
         <v>919</v>
@@ -15126,7 +15132,7 @@
         <v>999</v>
       </c>
       <c r="C151" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D151" s="6" t="s">
         <v>920</v>
@@ -15146,8 +15152,8 @@
       <c r="B152" s="6" t="s">
         <v>941</v>
       </c>
-      <c r="C152" s="6" t="s">
-        <v>2</v>
+      <c r="C152" t="s">
+        <v>3747</v>
       </c>
       <c r="D152" s="6" t="s">
         <v>951</v>
@@ -15168,7 +15174,7 @@
         <v>1000</v>
       </c>
       <c r="C153" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D153" s="6" t="s">
         <v>921</v>
@@ -15192,7 +15198,7 @@
         <v>1001</v>
       </c>
       <c r="C154" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D154" s="6" t="s">
         <v>922</v>
@@ -15216,7 +15222,7 @@
         <v>1002</v>
       </c>
       <c r="C155" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D155" s="6" t="s">
         <v>923</v>
@@ -15240,7 +15246,7 @@
         <v>1003</v>
       </c>
       <c r="C156" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D156" s="6" t="s">
         <v>924</v>
@@ -15264,7 +15270,7 @@
         <v>1004</v>
       </c>
       <c r="C157" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D157" s="6" t="s">
         <v>925</v>
@@ -15284,8 +15290,8 @@
       <c r="B158" s="6" t="s">
         <v>942</v>
       </c>
-      <c r="C158" s="6" t="s">
-        <v>2</v>
+      <c r="C158" t="s">
+        <v>3747</v>
       </c>
       <c r="D158" s="6" t="s">
         <v>952</v>
@@ -15306,7 +15312,7 @@
         <v>1005</v>
       </c>
       <c r="C159" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D159" s="6" t="s">
         <v>926</v>
@@ -15330,7 +15336,7 @@
         <v>1006</v>
       </c>
       <c r="C160" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D160" s="6" t="s">
         <v>927</v>
@@ -15354,7 +15360,7 @@
         <v>1007</v>
       </c>
       <c r="C161" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D161" s="6" t="s">
         <v>928</v>
@@ -15378,7 +15384,7 @@
         <v>1008</v>
       </c>
       <c r="C162" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D162" s="6" t="s">
         <v>929</v>
@@ -15398,8 +15404,8 @@
       <c r="B163" s="6" t="s">
         <v>943</v>
       </c>
-      <c r="C163" s="6" t="s">
-        <v>2</v>
+      <c r="C163" t="s">
+        <v>3747</v>
       </c>
       <c r="D163" s="6" t="s">
         <v>953</v>
@@ -15420,7 +15426,7 @@
         <v>1009</v>
       </c>
       <c r="C164" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D164" s="6" t="s">
         <v>930</v>
@@ -15444,7 +15450,7 @@
         <v>1010</v>
       </c>
       <c r="C165" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D165" s="6" t="s">
         <v>931</v>
@@ -15468,7 +15474,7 @@
         <v>1011</v>
       </c>
       <c r="C166" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D166" s="6" t="s">
         <v>932</v>
@@ -15488,8 +15494,8 @@
       <c r="B167" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="C167" s="6" t="s">
-        <v>2</v>
+      <c r="C167" t="s">
+        <v>3747</v>
       </c>
       <c r="D167" s="6" t="s">
         <v>954</v>
@@ -15510,7 +15516,7 @@
         <v>1012</v>
       </c>
       <c r="C168" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D168" s="6" t="s">
         <v>933</v>
@@ -15534,7 +15540,7 @@
         <v>1013</v>
       </c>
       <c r="C169" t="s">
-        <v>2</v>
+        <v>3747</v>
       </c>
       <c r="D169" s="6" t="s">
         <v>934</v>
@@ -15554,8 +15560,8 @@
       <c r="B170" s="6" t="s">
         <v>945</v>
       </c>
-      <c r="C170" s="6" t="s">
-        <v>2</v>
+      <c r="C170" t="s">
+        <v>3747</v>
       </c>
       <c r="D170" s="6" t="s">
         <v>955</v>
@@ -18063,7 +18069,7 @@
         <v>1094</v>
       </c>
       <c r="C291" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D291" s="6" t="s">
         <v>1032</v>
@@ -18080,7 +18086,7 @@
         <v>1014</v>
       </c>
       <c r="C292" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D292" s="6" t="s">
         <v>1025</v>
@@ -18100,7 +18106,7 @@
         <v>1015</v>
       </c>
       <c r="C293" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D293" s="6" t="s">
         <v>1026</v>
@@ -18119,7 +18125,7 @@
         <v>1016</v>
       </c>
       <c r="C294" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D294" s="6" t="s">
         <v>1027</v>
@@ -18138,7 +18144,7 @@
         <v>1017</v>
       </c>
       <c r="C295" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D295" s="6" t="s">
         <v>1028</v>
@@ -18156,7 +18162,7 @@
         <v>1018</v>
       </c>
       <c r="C296" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D296" s="6" t="s">
         <v>1029</v>
@@ -18174,7 +18180,7 @@
         <v>1019</v>
       </c>
       <c r="C297" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D297" s="6" t="s">
         <v>1030</v>
@@ -18192,7 +18198,7 @@
         <v>1020</v>
       </c>
       <c r="C298" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D298" s="6" t="s">
         <v>1031</v>
@@ -18210,7 +18216,7 @@
         <v>1021</v>
       </c>
       <c r="C299" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D299" s="6" t="s">
         <v>1032</v>
@@ -18228,7 +18234,7 @@
         <v>1115</v>
       </c>
       <c r="C300" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D300" s="6" t="s">
         <v>1033</v>
@@ -18248,7 +18254,7 @@
         <v>1116</v>
       </c>
       <c r="C301" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D301" s="6" t="s">
         <v>1034</v>
@@ -18268,7 +18274,7 @@
         <v>1117</v>
       </c>
       <c r="C302" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D302" s="6" t="s">
         <v>1035</v>
@@ -18288,7 +18294,7 @@
         <v>1118</v>
       </c>
       <c r="C303" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D303" s="6" t="s">
         <v>1036</v>
@@ -18308,7 +18314,7 @@
         <v>1119</v>
       </c>
       <c r="C304" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D304" s="6" t="s">
         <v>1037</v>
@@ -18328,7 +18334,7 @@
         <v>1120</v>
       </c>
       <c r="C305" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D305" s="6" t="s">
         <v>1038</v>
@@ -18349,7 +18355,7 @@
         <v>1022</v>
       </c>
       <c r="C306" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D306" s="6" t="s">
         <v>1039</v>
@@ -18369,7 +18375,7 @@
         <v>1095</v>
       </c>
       <c r="C307" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D307" s="6" t="s">
         <v>1105</v>
@@ -18386,7 +18392,7 @@
         <v>1121</v>
       </c>
       <c r="C308" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D308" s="6" t="s">
         <v>1040</v>
@@ -18403,7 +18409,7 @@
         <v>1122</v>
       </c>
       <c r="C309" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D309" s="6" t="s">
         <v>1041</v>
@@ -18420,7 +18426,7 @@
         <v>1096</v>
       </c>
       <c r="C310" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D310" s="6" t="s">
         <v>1106</v>
@@ -18437,7 +18443,7 @@
         <v>1123</v>
       </c>
       <c r="C311" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D311" s="6" t="s">
         <v>1042</v>
@@ -18457,7 +18463,7 @@
         <v>1124</v>
       </c>
       <c r="C312" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D312" s="6" t="s">
         <v>1043</v>
@@ -18477,7 +18483,7 @@
         <v>1125</v>
       </c>
       <c r="C313" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D313" s="6" t="s">
         <v>1044</v>
@@ -18497,7 +18503,7 @@
         <v>1126</v>
       </c>
       <c r="C314" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D314" s="6" t="s">
         <v>1045</v>
@@ -18517,7 +18523,7 @@
         <v>1127</v>
       </c>
       <c r="C315" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D315" s="6" t="s">
         <v>1046</v>
@@ -18537,7 +18543,7 @@
         <v>1128</v>
       </c>
       <c r="C316" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D316" s="6" t="s">
         <v>1047</v>
@@ -18557,7 +18563,7 @@
         <v>1023</v>
       </c>
       <c r="C317" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D317" s="6" t="s">
         <v>1048</v>
@@ -18574,7 +18580,7 @@
         <v>1097</v>
       </c>
       <c r="C318" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D318" s="6" t="s">
         <v>1107</v>
@@ -18591,7 +18597,7 @@
         <v>1129</v>
       </c>
       <c r="C319" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D319" s="6" t="s">
         <v>1049</v>
@@ -18614,7 +18620,7 @@
         <v>1130</v>
       </c>
       <c r="C320" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D320" s="6" t="s">
         <v>1050</v>
@@ -18637,7 +18643,7 @@
         <v>1131</v>
       </c>
       <c r="C321" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D321" s="6" t="s">
         <v>1051</v>
@@ -18660,7 +18666,7 @@
         <v>1132</v>
       </c>
       <c r="C322" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D322" s="6" t="s">
         <v>1052</v>
@@ -18683,7 +18689,7 @@
         <v>1133</v>
       </c>
       <c r="C323" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D323" s="6" t="s">
         <v>1053</v>
@@ -18706,7 +18712,7 @@
         <v>1134</v>
       </c>
       <c r="C324" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D324" s="6" t="s">
         <v>1054</v>
@@ -18729,7 +18735,7 @@
         <v>1135</v>
       </c>
       <c r="C325" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D325" s="6" t="s">
         <v>1055</v>
@@ -18753,7 +18759,7 @@
         <v>1136</v>
       </c>
       <c r="C326" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D326" s="6" t="s">
         <v>1056</v>
@@ -18776,7 +18782,7 @@
         <v>1137</v>
       </c>
       <c r="C327" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D327" s="6" t="s">
         <v>1057</v>
@@ -18799,7 +18805,7 @@
         <v>1138</v>
       </c>
       <c r="C328" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D328" s="6" t="s">
         <v>1058</v>
@@ -18822,7 +18828,7 @@
         <v>1139</v>
       </c>
       <c r="C329" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D329" s="6" t="s">
         <v>1059</v>
@@ -18846,7 +18852,7 @@
         <v>1140</v>
       </c>
       <c r="C330" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D330" s="6" t="s">
         <v>1060</v>
@@ -18870,7 +18876,7 @@
         <v>1141</v>
       </c>
       <c r="C331" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D331" s="6" t="s">
         <v>1061</v>
@@ -18891,7 +18897,7 @@
         <v>1098</v>
       </c>
       <c r="C332" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D332" s="6" t="s">
         <v>1108</v>
@@ -18912,7 +18918,7 @@
         <v>1142</v>
       </c>
       <c r="C333" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D333" s="6" t="s">
         <v>1062</v>
@@ -18932,7 +18938,7 @@
         <v>1143</v>
       </c>
       <c r="C334" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D334" s="6" t="s">
         <v>1063</v>
@@ -18955,7 +18961,7 @@
         <v>1144</v>
       </c>
       <c r="C335" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D335" s="6" t="s">
         <v>1064</v>
@@ -18978,7 +18984,7 @@
         <v>1145</v>
       </c>
       <c r="C336" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D336" s="6" t="s">
         <v>1065</v>
@@ -19001,7 +19007,7 @@
         <v>1146</v>
       </c>
       <c r="C337" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D337" s="6" t="s">
         <v>1066</v>
@@ -19024,7 +19030,7 @@
         <v>1024</v>
       </c>
       <c r="C338" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D338" s="6" t="s">
         <v>1067</v>
@@ -19047,7 +19053,7 @@
         <v>1099</v>
       </c>
       <c r="C339" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D339" s="6" t="s">
         <v>1109</v>
@@ -19068,7 +19074,7 @@
         <v>1147</v>
       </c>
       <c r="C340" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D340" s="6" t="s">
         <v>1068</v>
@@ -19089,7 +19095,7 @@
         <v>1148</v>
       </c>
       <c r="C341" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D341" s="6" t="s">
         <v>1069</v>
@@ -19112,7 +19118,7 @@
         <v>1149</v>
       </c>
       <c r="C342" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D342" s="6" t="s">
         <v>1070</v>
@@ -19135,7 +19141,7 @@
         <v>1150</v>
       </c>
       <c r="C343" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D343" s="6" t="s">
         <v>1071</v>
@@ -19158,7 +19164,7 @@
         <v>1151</v>
       </c>
       <c r="C344" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D344" s="6" t="s">
         <v>1072</v>
@@ -19181,7 +19187,7 @@
         <v>1152</v>
       </c>
       <c r="C345" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D345" s="6" t="s">
         <v>1073</v>
@@ -19204,7 +19210,7 @@
         <v>1153</v>
       </c>
       <c r="C346" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D346" s="6" t="s">
         <v>1074</v>
@@ -19228,7 +19234,7 @@
         <v>1154</v>
       </c>
       <c r="C347" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D347" s="6" t="s">
         <v>1075</v>
@@ -19252,7 +19258,7 @@
         <v>1155</v>
       </c>
       <c r="C348" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D348" s="6" t="s">
         <v>1076</v>
@@ -19276,7 +19282,7 @@
         <v>1156</v>
       </c>
       <c r="C349" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D349" s="6" t="s">
         <v>1077</v>
@@ -19300,7 +19306,7 @@
         <v>1157</v>
       </c>
       <c r="C350" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D350" s="6" t="s">
         <v>1078</v>
@@ -19324,7 +19330,7 @@
         <v>1100</v>
       </c>
       <c r="C351" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D351" s="6" t="s">
         <v>1110</v>
@@ -19345,7 +19351,7 @@
         <v>1158</v>
       </c>
       <c r="C352" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D352" s="6" t="s">
         <v>1079</v>
@@ -19365,7 +19371,7 @@
         <v>1159</v>
       </c>
       <c r="C353" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D353" s="6" t="s">
         <v>1080</v>
@@ -19388,7 +19394,7 @@
         <v>1160</v>
       </c>
       <c r="C354" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D354" s="6" t="s">
         <v>1081</v>
@@ -19411,7 +19417,7 @@
         <v>1161</v>
       </c>
       <c r="C355" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D355" s="6" t="s">
         <v>1082</v>
@@ -19434,7 +19440,7 @@
         <v>1162</v>
       </c>
       <c r="C356" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D356" s="6" t="s">
         <v>1083</v>
@@ -19457,7 +19463,7 @@
         <v>1101</v>
       </c>
       <c r="C357" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D357" s="6" t="s">
         <v>1111</v>
@@ -19477,7 +19483,7 @@
         <v>1163</v>
       </c>
       <c r="C358" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D358" s="6" t="s">
         <v>1084</v>
@@ -19497,7 +19503,7 @@
         <v>1164</v>
       </c>
       <c r="C359" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D359" s="6" t="s">
         <v>1085</v>
@@ -19520,7 +19526,7 @@
         <v>1165</v>
       </c>
       <c r="C360" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D360" s="6" t="s">
         <v>1086</v>
@@ -19543,7 +19549,7 @@
         <v>1166</v>
       </c>
       <c r="C361" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D361" s="6" t="s">
         <v>1087</v>
@@ -19566,7 +19572,7 @@
         <v>1102</v>
       </c>
       <c r="C362" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D362" s="6" t="s">
         <v>1112</v>
@@ -19586,7 +19592,7 @@
         <v>1167</v>
       </c>
       <c r="C363" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D363" s="6" t="s">
         <v>1088</v>
@@ -19606,7 +19612,7 @@
         <v>1168</v>
       </c>
       <c r="C364" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D364" s="6" t="s">
         <v>1089</v>
@@ -19629,7 +19635,7 @@
         <v>1169</v>
       </c>
       <c r="C365" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D365" s="6" t="s">
         <v>1090</v>
@@ -19652,7 +19658,7 @@
         <v>1103</v>
       </c>
       <c r="C366" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D366" s="6" t="s">
         <v>1113</v>
@@ -19672,7 +19678,7 @@
         <v>1170</v>
       </c>
       <c r="C367" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D367" s="6" t="s">
         <v>1091</v>
@@ -19692,7 +19698,7 @@
         <v>1171</v>
       </c>
       <c r="C368" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D368" s="6" t="s">
         <v>1092</v>
@@ -19715,7 +19721,7 @@
         <v>1172</v>
       </c>
       <c r="C369" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D369" s="6" t="s">
         <v>1093</v>
@@ -19735,7 +19741,7 @@
         <v>1104</v>
       </c>
       <c r="C370" t="s">
-        <v>11</v>
+        <v>3748</v>
       </c>
       <c r="D370" s="6" t="s">
         <v>1114</v>
